--- a/Examples/orcvcr/orcvcr_model.xlsx
+++ b/Examples/orcvcr/orcvcr_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ctorr\Documents\Proyectos\TaesLab\Examples\orcvcr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842223AB-1DC9-41CD-9BC5-31898B8E4676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1838FABF-A869-4526-924B-CDA499E9086F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="435" windowWidth="25740" windowHeight="14700" firstSheet="1" activeTab="3" xr2:uid="{E29BBF69-888A-4B0D-A36F-5F6BD99DC033}"/>
+    <workbookView xWindow="5460" yWindow="765" windowWidth="22965" windowHeight="14700" firstSheet="2" activeTab="4" xr2:uid="{E29BBF69-888A-4B0D-A36F-5F6BD99DC033}"/>
   </bookViews>
   <sheets>
     <sheet name="Physical Diagram" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <sheet name="WasteAllocation" sheetId="8" r:id="rId8"/>
     <sheet name="ResourcesCost" sheetId="9" r:id="rId9"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
   <definedNames>
     <definedName name="DATOS" localSheetId="4">Exergy!#REF!</definedName>
     <definedName name="tgas_fmt" localSheetId="5">Format!$A$1:$D$7</definedName>
@@ -63,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="87">
   <si>
     <t>Flows</t>
   </si>
@@ -236,12 +239,6 @@
     <t>(B2-B3)+(B8-B5)</t>
   </si>
   <si>
-    <t>WT-WC</t>
-  </si>
-  <si>
-    <t>WN+WP</t>
-  </si>
-  <si>
     <t>B4-B3</t>
   </si>
   <si>
@@ -314,16 +311,22 @@
     <t>ETAC75</t>
   </si>
   <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>TBLR85</t>
+  </si>
+  <si>
+    <t>WC+WP+WN</t>
+  </si>
+  <si>
+    <t>WN200</t>
+  </si>
+  <si>
     <t>TCND35</t>
   </si>
   <si>
-    <t>CG</t>
-  </si>
-  <si>
-    <t>TBLR85</t>
-  </si>
-  <si>
-    <t>W200</t>
+    <t>WN0</t>
   </si>
 </sst>
 </file>
@@ -462,6 +465,126 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="REF"/>
+      <sheetName val="ETAT75"/>
+      <sheetName val="ETAC75"/>
+      <sheetName val="TCND35"/>
+      <sheetName val="TBLR85"/>
+      <sheetName val="WN200"/>
+      <sheetName val="Exergy"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>key</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>B1</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>B2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>B3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>B4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>B5</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>B6</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>B7</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>B8</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>WT</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>WC</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>WP</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>QBLR</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>QEVP</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>WN</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>QCND</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>QEXP</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5">
+        <row r="2">
+          <cell r="G2">
+            <v>1178</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -993,7 +1116,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1001,7 +1124,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1032,6 +1155,7 @@
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" customWidth="1"/>
   </cols>
@@ -1078,7 +1202,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
@@ -1098,7 +1222,7 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>47</v>
@@ -1115,7 +1239,7 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>48</v>
@@ -1129,7 +1253,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -1146,10 +1270,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
         <v>51</v>
@@ -1163,10 +1287,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
         <v>49</v>
@@ -1208,127 +1332,148 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C71C192-3DC3-406B-9DFF-73A67AE08F6E}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>19</v>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="str">
+        <f>[1]REF!A1</f>
+        <v>key</v>
       </c>
       <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" t="s">
         <v>80</v>
       </c>
-      <c r="C1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" t="s">
         <v>82</v>
-      </c>
-      <c r="E1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" t="s">
-        <v>85</v>
       </c>
       <c r="G1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>21</v>
+      <c r="H1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="str">
+        <f>[1]REF!A2</f>
+        <v>B1</v>
       </c>
       <c r="B2">
-        <v>617.20000000000005</v>
+        <v>684.6</v>
       </c>
       <c r="C2">
-        <v>661.3</v>
+        <v>733.5</v>
       </c>
       <c r="D2">
-        <v>617.20000000000005</v>
+        <v>684.6</v>
       </c>
       <c r="E2">
-        <v>690.1</v>
+        <v>765.4</v>
       </c>
       <c r="F2">
-        <v>637.5</v>
+        <v>707.1</v>
       </c>
       <c r="G2">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
+        <v>629.79999999999995</v>
+      </c>
+      <c r="H2">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <f>[1]REF!A3</f>
+        <v>B2</v>
       </c>
       <c r="B3">
-        <v>315.3</v>
+        <v>349.7</v>
       </c>
       <c r="C3">
-        <v>339.1</v>
+        <v>376.1</v>
       </c>
       <c r="D3">
-        <v>315.3</v>
+        <v>349.7</v>
       </c>
       <c r="E3">
-        <v>387.3</v>
+        <v>429.6</v>
       </c>
       <c r="F3">
-        <v>336.5</v>
+        <v>373.3</v>
       </c>
       <c r="G3">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
+        <v>321.7</v>
+      </c>
+      <c r="H3">
+        <v>601.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
+        <f>[1]REF!A4</f>
+        <v>B3</v>
       </c>
       <c r="B4">
-        <v>246.9</v>
+        <v>273.8</v>
       </c>
       <c r="C4">
-        <v>264.5</v>
+        <v>293.39999999999998</v>
       </c>
       <c r="D4">
-        <v>246.9</v>
+        <v>273.8</v>
       </c>
       <c r="E4">
-        <v>279.8</v>
+        <v>310.39999999999998</v>
       </c>
       <c r="F4">
-        <v>264.3</v>
+        <v>293.10000000000002</v>
       </c>
       <c r="G4">
-        <v>465.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>24</v>
+        <v>251.9</v>
+      </c>
+      <c r="H4">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
+        <f>[1]REF!A5</f>
+        <v>B4</v>
       </c>
       <c r="B5">
-        <v>259.5</v>
+        <v>287.89999999999998</v>
       </c>
       <c r="C5">
-        <v>278.10000000000002</v>
+        <v>308.39999999999998</v>
       </c>
       <c r="D5">
-        <v>259.5</v>
+        <v>287.89999999999998</v>
       </c>
       <c r="E5">
-        <v>293.5</v>
+        <v>325.5</v>
       </c>
       <c r="F5">
-        <v>276.2</v>
+        <v>306.3</v>
       </c>
       <c r="G5">
-        <v>489.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>25</v>
+        <v>264.8</v>
+      </c>
+      <c r="H5">
+        <v>495.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <f>[1]REF!A6</f>
+        <v>B5</v>
       </c>
       <c r="B6">
         <v>193.5</v>
@@ -1348,10 +1493,14 @@
       <c r="G6">
         <v>193.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
+      <c r="H6">
+        <v>193.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f>[1]REF!A7</f>
+        <v>B6</v>
       </c>
       <c r="B7">
         <v>167.2</v>
@@ -1371,10 +1520,14 @@
       <c r="G7">
         <v>167.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
+      <c r="H7">
+        <v>167.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <f>[1]REF!A8</f>
+        <v>B7</v>
       </c>
       <c r="B8">
         <v>55.19</v>
@@ -1394,10 +1547,14 @@
       <c r="G8">
         <v>55.19</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>28</v>
+      <c r="H8">
+        <v>55.19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <f>[1]REF!A9</f>
+        <v>B8</v>
       </c>
       <c r="B9">
         <v>240.8</v>
@@ -1417,33 +1574,41 @@
       <c r="G9">
         <v>240.8</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>29</v>
+      <c r="H9">
+        <v>240.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f>[1]REF!A10</f>
+        <v>WT</v>
       </c>
       <c r="B10">
-        <v>245.1</v>
+        <v>271.89999999999998</v>
       </c>
       <c r="C10">
-        <v>246.2</v>
+        <v>273.10000000000002</v>
       </c>
       <c r="D10">
-        <v>245.1</v>
+        <v>271.89999999999998</v>
       </c>
       <c r="E10">
-        <v>246.3</v>
+        <v>273.10000000000002</v>
       </c>
       <c r="F10">
-        <v>244.2</v>
+        <v>270.8</v>
       </c>
       <c r="G10">
-        <v>462.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>30</v>
+        <v>250.1</v>
+      </c>
+      <c r="H10">
+        <v>467.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <f>[1]REF!A11</f>
+        <v>WC</v>
       </c>
       <c r="B11">
         <v>230</v>
@@ -1463,56 +1628,68 @@
       <c r="G11">
         <v>230</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>31</v>
+      <c r="H11">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <f>[1]REF!A12</f>
+        <v>WP</v>
       </c>
       <c r="B12">
-        <v>14.81</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="C12">
-        <v>15.86</v>
+        <v>17.59</v>
       </c>
       <c r="D12">
-        <v>14.81</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="E12">
-        <v>15.94</v>
+        <v>17.68</v>
       </c>
       <c r="F12">
-        <v>13.87</v>
+        <v>15.39</v>
       </c>
       <c r="G12">
-        <v>27.94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>53</v>
+        <v>15.11</v>
+      </c>
+      <c r="H12">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f>[1]REF!A13</f>
+        <v>QBLR</v>
       </c>
       <c r="B13">
-        <v>491</v>
+        <v>545.79999999999995</v>
       </c>
       <c r="C13">
-        <v>526</v>
+        <v>584.79999999999995</v>
       </c>
       <c r="D13">
-        <v>491</v>
+        <v>545.79999999999995</v>
       </c>
       <c r="E13">
-        <v>537.1</v>
+        <v>597</v>
       </c>
       <c r="F13">
-        <v>507.9</v>
+        <v>564.6</v>
       </c>
       <c r="G13">
-        <v>926.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>32</v>
+        <v>502.1</v>
+      </c>
+      <c r="H13">
+        <v>938.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <f>[1]REF!A14</f>
+        <v>QEVP</v>
       </c>
       <c r="B14">
         <v>42.96</v>
@@ -1532,74 +1709,103 @@
       <c r="G14">
         <v>42.96</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>33</v>
+      <c r="H14">
+        <v>42.96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <f>[1]REF!A15</f>
+        <v>WN</v>
       </c>
       <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="F15">
+        <v>20</v>
+      </c>
+      <c r="G15">
         <v>0</v>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
+      <c r="H15">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>74</v>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <f>[1]REF!A16</f>
+        <v>QCND</v>
       </c>
       <c r="B16">
+        <f>B3+B9-B4-B6</f>
+        <v>123.19999999999999</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ref="C16:G16" si="0">C3+C9-C4-C6</f>
+        <v>130.00000000000011</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>121.00000000000003</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>180.10000000000002</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>127.5</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>117.10000000000002</v>
+      </c>
+      <c r="H16">
+        <f>H3+H9-H4-H6</f>
+        <v>177.70000000000005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <f>[1]REF!A17</f>
+        <v>QEXP</v>
+      </c>
+      <c r="B17">
+        <f>B6-B7</f>
         <v>26.300000000000011</v>
       </c>
-      <c r="C16">
+      <c r="C17">
+        <f t="shared" ref="C17:G17" si="1">C6-C7</f>
         <v>26.300000000000011</v>
       </c>
-      <c r="D16">
+      <c r="D17">
+        <f t="shared" si="1"/>
         <v>24.599999999999994</v>
       </c>
-      <c r="E16">
+      <c r="E17">
+        <f t="shared" si="1"/>
         <v>30.300000000000011</v>
       </c>
-      <c r="F16">
+      <c r="F17">
+        <f t="shared" si="1"/>
         <v>26.300000000000011</v>
       </c>
-      <c r="G16">
+      <c r="G17">
+        <f t="shared" si="1"/>
         <v>26.300000000000011</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17">
-        <v>115.70000000000005</v>
-      </c>
-      <c r="C17">
-        <v>121.90000000000003</v>
-      </c>
-      <c r="D17">
-        <v>113.49999999999997</v>
-      </c>
-      <c r="E17">
-        <v>168.39999999999998</v>
-      </c>
-      <c r="F17">
-        <v>119.5</v>
-      </c>
-      <c r="G17">
-        <v>176.40000000000003</v>
+      <c r="H17">
+        <f>H6-H7</f>
+        <v>26.300000000000011</v>
       </c>
     </row>
   </sheetData>
@@ -1620,13 +1826,13 @@
         <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1640,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -1654,12 +1860,12 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -1668,12 +1874,12 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1682,12 +1888,12 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -1696,12 +1902,12 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -1710,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1940,7 @@
         <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1742,7 +1948,7 @@
         <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1750,10 +1956,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1786,7 +1992,7 @@
         <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C1" t="s">
         <v>54</v>
@@ -1829,13 +2035,13 @@
         <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
